--- a/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.87%1,794,000</t>
+          <t>8.89%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.89%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.22%736,000</t>
+          <t>7.24%736,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>7.24%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.17%5,709,000</t>
+          <t>6.06%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.4%759</t>
+          <t>+2.11%775</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.57%3,697,000</t>
+          <t>5.54%3,700,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3697000</v>
+        <v>3700000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11835</v>
+        <v>2085</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.30%179,000</t>
+          <t>4.23%1,016,225</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>179000</v>
+        <v>1016225</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2110</v>
+        <v>12145</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.23%1,016,225</t>
+          <t>4.18%179,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1016225</v>
+        <v>179000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.65%933</t>
+          <t>+7.18%1000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+7.18%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>933</v>
+        <v>1000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.77%2,041,000</t>
+          <t>3.76%2,041,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.53%1,180,000</t>
+          <t>3.47%1,180,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.47%815,000</t>
+          <t>3.35%815,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.59%510</t>
+          <t>+10%561</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.19%3,158,000</t>
+          <t>3.18%3,158,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.85%5030</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5030</v>
+        <v>6290</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.07%301,000</t>
+          <t>3.08%251,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>301000</v>
+        <v>251000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>-1.85%5030</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6205</v>
+        <v>5030</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.97%251,000</t>
+          <t>2.99%301,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>251000</v>
+        <v>301000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.55%372,000</t>
+          <t>2.58%372,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:50</t>
+          <t>2026-10-02 19:05:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.23%1,082,000</t>
+          <t>2.32%1,082,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.79%284.5</t>
+          <t>-1.05%281.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>284.5</v>
+        <v>281.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.79%3,216,000</t>
+          <t>1.81%3,216,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.09%546</t>
+          <t>+6.23%580</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>+6.23%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.68%1,529,000</t>
+          <t>1.65%1,529,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.58%5,116,000</t>
+          <t>1.63%5,116,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.41%3,415,000</t>
+          <t>1.43%3,415,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.41%723</t>
+          <t>-0.97%716</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.39%964,000</t>
+          <t>1.38%964,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.55%19040</t>
+          <t>-2.1%186.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19040</v>
+        <v>186.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.34%35,900</t>
+          <t>1.37%3,638,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>35900</v>
+        <v>3638000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+3.25%190.5</t>
+          <t>+1.55%19040</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>190.5</v>
+        <v>19040</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.34%3,638,000</t>
+          <t>1.35%35,900</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3638000</v>
+        <v>35900</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.53%189</t>
+          <t>-0.26%188.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>189</v>
+        <v>188.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.29%3,438,000</t>
+          <t>1.28%3,438,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1900</v>
+        <v>1535</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.28%363,000</t>
+          <t>1.27%418,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>363000</v>
+        <v>418000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>+1.36%373.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1535</v>
+        <v>373.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.27%418,000</t>
+          <t>1.26%1,737,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>418000</v>
+        <v>1737000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.79%368.5</t>
+          <t>+1.56%97.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>368.5</v>
+        <v>97.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.24%1,737,000</t>
+          <t>1.23%6,382,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1737000</v>
+        <v>6382000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.54%185</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>185</v>
+        <v>713</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.24%3,345,000</t>
+          <t>1.23%876,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3345000</v>
+        <v>876000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>-0.54%185</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>710</v>
+        <v>185</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.23%876,000</t>
+          <t>1.22%3,345,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>876000</v>
+        <v>3345000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>+6.39%683</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+6.39%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1565</v>
+        <v>683</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.22%382,000</t>
+          <t>1.19%940,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>382000</v>
+        <v>940000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:52</t>
+          <t>2026-10-02 19:05:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.56%97.5</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>97.5</v>
+        <v>1510</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.22%6,382,000</t>
+          <t>1.18%382,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>6382000</v>
+        <v>382000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.78%261</t>
+          <t>+0.77%263</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%2,268,000</t>
+          <t>1.17%2,268,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%707</t>
+          <t>+5.3%308</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>707</v>
+        <v>308</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.11%790,000</t>
+          <t>1.10%1,910,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>790000</v>
+        <v>1910000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.04%292.5</t>
+          <t>+1.98%721</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>292.5</v>
+        <v>721</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.10%1,910,000</t>
+          <t>1.10%790,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1910000</v>
+        <v>790000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.74%543</t>
+          <t>+2.66%173.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>543</v>
+        <v>173.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.07%1,000,000</t>
+          <t>1.09%3,280,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000000</v>
+        <v>3280000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.97%169</t>
+          <t>+1.66%552</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.97%</t>
+          <t>+1.66%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>169</v>
+        <v>552</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.05%3,280,000</t>
+          <t>1.07%1,000,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>3280000</v>
+        <v>1000000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.75%124.5</t>
+          <t>+2.01%127</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>+2.01%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>124.5</v>
+        <v>127</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.04%4,331,000</t>
+          <t>1.06%4,331,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.99%152.5</t>
+          <t>+1.64%155</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>152.5</v>
+        <v>155</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.05%642</t>
+          <t>-2.1%420.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>642</v>
+        <v>420.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.92%740,000</t>
+          <t>0.88%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>740000</v>
+        <v>1032000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.3%429.5</t>
+          <t>+4.35%959</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>+4.35%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>429.5</v>
+        <v>959</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.87%1,032,000</t>
+          <t>0.86%455,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1032000</v>
+        <v>455000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.35%959</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.35%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>959</v>
+        <v>1965</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.83%455,000</t>
+          <t>0.83%222,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>455000</v>
+        <v>222000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+3.54%248.5</t>
+          <t>-1.41%245</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>248.5</v>
+        <v>245</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.77%1,607,000</t>
+          <t>0.79%1,607,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.61%93,000</t>
+          <t>0.60%93,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+9.89%405.5</t>
+          <t>+8.26%439</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+9.89%</t>
+          <t>+8.26%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>405.5</v>
+        <v>439</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.39%527,000</t>
+          <t>0.42%527,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.91%602</t>
+          <t>+2.66%618</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.35%304,000</t>
+          <t>0.36%304,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:53</t>
+          <t>2026-10-02 19:05:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%50.2</t>
+          <t>+1%50.7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>6640均華</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.4%123</t>
+          <t>+6.73%1110</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+6.73%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>123</v>
+        <v>1110</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.32%1,281,000</t>
+          <t>0.31%143,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1281000</v>
+        <v>143000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.41%243</t>
+          <t>+2.44%126</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.30%627,000</t>
+          <t>0.31%1,281,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>627000</v>
+        <v>1281000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,25 +3371,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.61%67.4</t>
+          <t>+0.21%243.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>67.40000000000001</v>
+        <v>243.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.30%2,213,556</t>
+          <t>0.30%627,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3398,11 +3398,11 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2213556</v>
+        <v>627000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6640均華</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+6.73%1110</t>
+          <t>-0.89%66.8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+6.73%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1110</v>
+        <v>66.8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.30%143,000</t>
+          <t>0.29%2,213,556</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>143000</v>
+        <v>2213556</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.7%1170</t>
+          <t>-0.43%1165</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+0.43%46.65</t>
+          <t>-1.39%46</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>46.65</v>
+        <v>46</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.87%170</t>
+          <t>0%170</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.72%688</t>
+          <t>+2.02%505</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>688</v>
+        <v>505</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,11 +3764,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+2.02%505</t>
+          <t>+0.58%692</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>505</v>
+        <v>692</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.61%48.85</t>
+          <t>0%48.85</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:54</t>
+          <t>2026-10-02 19:05:29</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-0.33%150.5</t>
+          <t>0%150.5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H58" t="n">

--- a/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:26</t>
+          <t>2026-10-02 22:49:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:27</t>
+          <t>2026-10-02 22:49:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:28</t>
+          <t>2026-10-02 22:49:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:29</t>
+          <t>2026-10-02 22:49:55</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:51</t>
+          <t>2026-10-02 22:58:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:52</t>
+          <t>2026-10-02 22:58:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:53</t>
+          <t>2026-10-02 22:58:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:55</t>
+          <t>2026-10-02 22:58:35</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:31</t>
+          <t>2026-10-02 23:48:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:33</t>
+          <t>2026-10-02 23:48:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:34</t>
+          <t>2026-10-02 23:48:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:35</t>
+          <t>2026-10-02 23:48:21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
